--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-22T13:00:39+00:00</t>
+    <t>2026-09-23T09:05:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T09:05:57+00:00</t>
+    <t>2026-09-23T11:48:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:48:18+00:00</t>
+    <t>2026-09-23T11:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:53:17+00:00</t>
+    <t>2026-09-23T11:53:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T11:53:51+00:00</t>
+    <t>2026-09-23T15:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
+++ b/main/ig/StructureDefinition-fr-lm-patient-summary-document.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T15:21:41+00:00</t>
+    <t>2026-09-25T08:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
